--- a/assets/operator_ids.xlsx
+++ b/assets/operator_ids.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GWE\git\gy454xe-decomp\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCCC78B-DB33-4AF5-A17D-ABB5A12306B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1601C81-AFB5-4104-84A6-09DC1C9C278C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2E85BE9C-B289-4076-84C1-7CA2746D82AC}"/>
   </bookViews>
@@ -738,9 +738,6 @@
     <t>Cube</t>
   </si>
   <si>
-    <t>x^-1 / Inverse matrix</t>
-  </si>
-  <si>
     <t>Multiply / Matrix cross product</t>
   </si>
   <si>
@@ -795,6 +792,9 @@
   </si>
   <si>
     <t>RanInt#(</t>
+  </si>
+  <si>
+    <t>Inverse</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1210,7 @@
     <col min="3" max="3" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="76.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2105,7 +2105,7 @@
         <v>0x2D</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>90</v>
@@ -3283,7 +3283,7 @@
         <v>0x6B</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>222</v>
@@ -3340,7 +3340,7 @@
         <v>0x6E</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>225</v>
@@ -3359,7 +3359,7 @@
         <v>0x6F</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>226</v>
@@ -3378,7 +3378,7 @@
         <v>0x70</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>227</v>
@@ -3397,7 +3397,7 @@
         <v>0x71</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>228</v>
@@ -3416,7 +3416,7 @@
         <v>0x72</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>229</v>
@@ -3435,7 +3435,7 @@
         <v>0x73</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>230</v>
@@ -3454,10 +3454,10 @@
         <v>0x74</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>101</v>
@@ -3473,16 +3473,16 @@
         <v>0x75</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3494,7 +3494,7 @@
         <v>0x76</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>231</v>
@@ -3513,10 +3513,10 @@
         <v>0x77</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>14</v>

--- a/assets/operator_ids.xlsx
+++ b/assets/operator_ids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GWE\git\gy454xe-decomp\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1601C81-AFB5-4104-84A6-09DC1C9C278C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CE7499-D201-402B-A6DC-FB762B94AFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2E85BE9C-B289-4076-84C1-7CA2746D82AC}"/>
   </bookViews>
@@ -776,9 +776,6 @@
     </r>
   </si>
   <si>
-    <t>Behaves similar to multiply. Purpose currently unknown; only used internally.</t>
-  </si>
-  <si>
     <t>???</t>
   </si>
   <si>
@@ -795,6 +792,9 @@
   </si>
   <si>
     <t>Inverse</t>
+  </si>
+  <si>
+    <t>Only used internally. Later set to multiply.</t>
   </si>
 </sst>
 </file>
@@ -3283,7 +3283,7 @@
         <v>0x6B</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>222</v>
@@ -3454,7 +3454,7 @@
         <v>0x74</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>241</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>0x75</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>242</v>
@@ -3482,7 +3482,7 @@
         <v>101</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3494,7 +3494,7 @@
         <v>0x76</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>231</v>
@@ -3513,10 +3513,10 @@
         <v>0x77</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>14</v>
